--- a/output/pdf_financials_xlsx/NVR.xlsx
+++ b/output/pdf_financials_xlsx/NVR.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.069808</v>
+        <v>-0.069808</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.07564800000000001</v>
+        <v>-0.07564800000000001</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.076362</v>
+        <v>-0.076362</v>
       </c>
     </row>
     <row r="17">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.069808</v>
+        <v>-0.069808</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.07564800000000001</v>
+        <v>-0.07564800000000001</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.076362</v>
+        <v>-0.076362</v>
       </c>
     </row>
     <row r="21">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.069808</v>
+        <v>-0.069808</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.07564800000000001</v>
+        <v>-0.07564800000000001</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.076362</v>
+        <v>-0.076362</v>
       </c>
     </row>
     <row r="24">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.069808</v>
+        <v>-0.069808</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.07564800000000001</v>
+        <v>-0.07564800000000001</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.076362</v>
+        <v>-0.076362</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.069808</v>
+        <v>-0.069808</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.07564800000000001</v>
+        <v>-0.07564800000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.076362</v>
+        <v>-0.076362</v>
       </c>
     </row>
     <row r="30">
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.058278</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.058278</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.065967</v>
       </c>
     </row>
     <row r="93">
@@ -3046,7 +3046,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3201,7 +3205,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>0.058278</v>
       </c>
@@ -3990,13 +3998,13 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.069808</v>
+        <v>-0.069808</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.07564800000000001</v>
+        <v>-0.07564800000000001</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.076362</v>
+        <v>-0.076362</v>
       </c>
     </row>
     <row r="44">

--- a/output/pdf_financials_xlsx/NVR.xlsx
+++ b/output/pdf_financials_xlsx/NVR.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.09825299999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.025393</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.110886</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.09825299999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.025393</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.110886</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.100738</v>
+        <v>0.002485</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.028052</v>
+        <v>0.002659</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.110886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/NVR.xlsx
+++ b/output/pdf_financials_xlsx/NVR.xlsx
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.015313</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.011999</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.018292</v>
       </c>
     </row>
     <row r="65">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="68">
